--- a/public/exports/68534917.xlsx
+++ b/public/exports/68534917.xlsx
@@ -131,16 +131,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719361, 2202685</t>
+          <t xml:space="preserve">259943, 259944, 259945, 259946, 259947, 259949, 259956, 259982, 259950, 259951, 259952, 259953, 259954, 259955, 259957, 259958, 259960, 259961, 259962, 259963, 259964, 259965, 259966, 259967, 259968, 259969, 259971, 259972, 259973, 259974, 259975, 259976, 259977, 259978, 259979, 259980, 259989, 259990, 259991, 259993, 259994, 259995</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F3">
-        <v>1537</v>
+        <v>3906</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -181,16 +181,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942071</t>
+          <t xml:space="preserve">267144, 267145</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F4">
-        <v>260</v>
+        <v>4890</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,30 +231,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942075</t>
+          <t xml:space="preserve">719361, 2202685</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F5">
-        <v>540</v>
+        <v>1537</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016090</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-26</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -281,30 +281,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203386</t>
+          <t xml:space="preserve">8942071</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F6">
-        <v>1115</v>
+        <v>260</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047379</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-29</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -331,25 +331,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">8942075</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F7">
-        <v>1586</v>
+        <v>540</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055903</t>
+          <t xml:space="preserve">200016078</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2019-06-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -381,25 +381,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203980</t>
+          <t xml:space="preserve">2203386</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>1771</v>
+        <v>1115</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">311156883</t>
+          <t xml:space="preserve">200047379</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-03</t>
+          <t xml:space="preserve">2021-03-29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -431,35 +431,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204990</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F9">
-        <v>280</v>
+        <v>1586</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211741</t>
+          <t xml:space="preserve">200055903</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -481,35 +481,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">2203980</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F10">
-        <v>355</v>
+        <v>1771</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214136</t>
+          <t xml:space="preserve">311156883</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-02-03</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188168</t>
+          <t xml:space="preserve">2204990</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="F11">
-        <v>792</v>
+        <v>280</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217330</t>
+          <t xml:space="preserve">311211741</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-13</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -581,25 +581,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203431</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F12">
-        <v>2288</v>
+        <v>355</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217395</t>
+          <t xml:space="preserve">311214136</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-13</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203441</t>
+          <t xml:space="preserve">2188168</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -640,11 +640,11 @@
         </is>
       </c>
       <c r="F13">
-        <v>839</v>
+        <v>792</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217448</t>
+          <t xml:space="preserve">311217330</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -681,20 +681,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203865</t>
+          <t xml:space="preserve">2203431</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F14">
-        <v>501</v>
+        <v>2288</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217456</t>
+          <t xml:space="preserve">311217395</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">100036252</t>
+          <t xml:space="preserve">2203441</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -740,16 +740,16 @@
         </is>
       </c>
       <c r="F15">
-        <v>1252</v>
+        <v>839</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217682</t>
+          <t xml:space="preserve">311217448</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-14</t>
+          <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -781,25 +781,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188167</t>
+          <t xml:space="preserve">2203865</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F16">
-        <v>383</v>
+        <v>501</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217631</t>
+          <t xml:space="preserve">311217456</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-14</t>
+          <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203336</t>
+          <t xml:space="preserve">100036252</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -840,11 +840,11 @@
         </is>
       </c>
       <c r="F17">
-        <v>3581</v>
+        <v>1252</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217669</t>
+          <t xml:space="preserve">311217682</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2187966</t>
+          <t xml:space="preserve">2188167</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -890,16 +890,16 @@
         </is>
       </c>
       <c r="F18">
-        <v>260</v>
+        <v>383</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217802</t>
+          <t xml:space="preserve">311217631</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-15</t>
+          <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204117</t>
+          <t xml:space="preserve">2203336</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="F19">
-        <v>875</v>
+        <v>3581</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217827</t>
+          <t xml:space="preserve">311217669</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-15</t>
+          <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">2187966</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="F20">
-        <v>1690</v>
+        <v>260</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224721</t>
+          <t xml:space="preserve">311217802</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-26</t>
+          <t xml:space="preserve">2026-12-15</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1031,25 +1031,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">2204117</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F21">
-        <v>295</v>
+        <v>875</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224732</t>
+          <t xml:space="preserve">311217827</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-26</t>
+          <t xml:space="preserve">2026-12-15</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1086,15 +1086,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F22">
-        <v>1384</v>
+        <v>1690</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224734</t>
+          <t xml:space="preserve">311224721</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1136,15 +1136,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F23">
-        <v>975</v>
+        <v>295</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224736</t>
+          <t xml:space="preserve">311224732</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F24">
-        <v>1102</v>
+        <v>1384</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224724</t>
+          <t xml:space="preserve">311224734</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1236,15 +1236,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F25">
-        <v>1102</v>
+        <v>975</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224727</t>
+          <t xml:space="preserve">311224736</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1286,15 +1286,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F26">
-        <v>772</v>
+        <v>1102</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224729</t>
+          <t xml:space="preserve">311224724</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1331,25 +1331,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190312</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F27">
-        <v>11134</v>
+        <v>1102</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231085</t>
+          <t xml:space="preserve">311224727</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-28</t>
+          <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1381,25 +1381,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942093</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F28">
-        <v>718</v>
+        <v>772</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238100</t>
+          <t xml:space="preserve">311224729</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1431,25 +1431,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">2190312</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F29">
-        <v>308</v>
+        <v>11134</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238368</t>
+          <t xml:space="preserve">311231085</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-02</t>
+          <t xml:space="preserve">2027-02-28</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">8942093</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="F30">
-        <v>775</v>
+        <v>718</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238367</t>
+          <t xml:space="preserve">311238097</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-02</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1531,20 +1531,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942071</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F31">
-        <v>11333</v>
+        <v>308</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238369</t>
+          <t xml:space="preserve">311238368</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1581,25 +1581,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189961</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F32">
-        <v>719</v>
+        <v>775</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238422</t>
+          <t xml:space="preserve">311238367</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1631,25 +1631,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190233</t>
+          <t xml:space="preserve">8942071</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F33">
-        <v>609</v>
+        <v>11333</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238569</t>
+          <t xml:space="preserve">311238369</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1681,20 +1681,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">2189961</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F34">
-        <v>1637</v>
+        <v>719</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238556</t>
+          <t xml:space="preserve">311238422</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1731,20 +1731,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">2190233</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F35">
-        <v>2297</v>
+        <v>609</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238556</t>
+          <t xml:space="preserve">311238569</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1786,11 +1786,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F36">
-        <v>2065</v>
+        <v>1637</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1836,15 +1836,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F37">
-        <v>2177</v>
+        <v>2297</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238554</t>
+          <t xml:space="preserve">311238556</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1881,20 +1881,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941976</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F38">
-        <v>2266</v>
+        <v>2065</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238551</t>
+          <t xml:space="preserve">311238556</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1931,20 +1931,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941976</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F39">
-        <v>1889</v>
+        <v>2177</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238551</t>
+          <t xml:space="preserve">311238554</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942017</t>
+          <t xml:space="preserve">8941976</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1990,11 +1990,11 @@
         </is>
       </c>
       <c r="F40">
-        <v>2149</v>
+        <v>2266</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238600</t>
+          <t xml:space="preserve">311238551</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2031,20 +2031,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942071</t>
+          <t xml:space="preserve">8941976</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F41">
-        <v>1724</v>
+        <v>1889</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238574</t>
+          <t xml:space="preserve">311238551</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">100003759</t>
+          <t xml:space="preserve">8942017</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2090,16 +2090,16 @@
         </is>
       </c>
       <c r="F42">
-        <v>431</v>
+        <v>2149</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238740</t>
+          <t xml:space="preserve">311238600</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-04</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189963</t>
+          <t xml:space="preserve">8942071</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F43">
-        <v>350</v>
+        <v>1724</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238698</t>
+          <t xml:space="preserve">311238574</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-04</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2202814</t>
+          <t xml:space="preserve">100003759</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2190,11 +2190,11 @@
         </is>
       </c>
       <c r="F44">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238728</t>
+          <t xml:space="preserve">311238740</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">267144, 267145</t>
+          <t xml:space="preserve">2189963</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2240,11 +2240,11 @@
         </is>
       </c>
       <c r="F45">
-        <v>4890</v>
+        <v>350</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238723</t>
+          <t xml:space="preserve">311238698</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942087</t>
+          <t xml:space="preserve">2202814</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2290,11 +2290,11 @@
         </is>
       </c>
       <c r="F46">
-        <v>1902</v>
+        <v>381</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238732</t>
+          <t xml:space="preserve">311238728</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2336,15 +2336,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F47">
-        <v>2493</v>
+        <v>1902</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238734</t>
+          <t xml:space="preserve">311238732</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">8942087</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F48">
-        <v>1789</v>
+        <v>2493</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298684</t>
+          <t xml:space="preserve">311238734</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-20</t>
+          <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2436,11 +2436,11 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F49">
-        <v>1339</v>
+        <v>1789</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2486,11 +2486,11 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F50">
-        <v>1448</v>
+        <v>1339</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2531,25 +2531,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7717401</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F51">
-        <v>1372</v>
+        <v>1448</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311453702</t>
+          <t xml:space="preserve">311298684</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-11</t>
+          <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203235</t>
+          <t xml:space="preserve">7717401</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2590,16 +2590,16 @@
         </is>
       </c>
       <c r="F52">
-        <v>339</v>
+        <v>1372</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519279</t>
+          <t xml:space="preserve">311453702</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-10</t>
+          <t xml:space="preserve">2030-08-11</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188346</t>
+          <t xml:space="preserve">2203235</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F53">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549361</t>
+          <t xml:space="preserve">311519279</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2031-05-10</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2206014</t>
+          <t xml:space="preserve">2188346</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F54">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668910</t>
+          <t xml:space="preserve">311549329</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-24</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">259943, 259944, 259945, 259946, 259947, 259949, 259956, 259982, 259950, 259951, 259952, 259953, 259954, 259955, 259957, 259958, 259960, 259961, 259962, 259963, 259964, 259965, 259966, 259967, 259968, 259969, 259971, 259972, 259973, 259974, 259975, 259976, 259977, 259978, 259979, 259980, 259989, 259990, 259991, 259993, 259994, 259995</t>
+          <t xml:space="preserve">2206014</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F55">
-        <v>3906</v>
+        <v>291</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903759</t>
+          <t xml:space="preserve">311668910</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2033-03-24</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">

--- a/public/exports/68534917.xlsx
+++ b/public/exports/68534917.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:L55"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Solrød Center 1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2203336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>260</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egeparken 33A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">259943, 259944, 259945, 259946, 259947, 259949, 259956, 259982, 259950, 259951, 259952, 259953, 259954, 259955, 259957, 259958, 259960, 259961, 259962, 259963, 259964, 259965, 259966, 259967, 259968, 259969, 259971, 259972, 259973, 259974, 259975, 259976, 259977, 259978, 259979, 259980, 259989, 259990, 259991, 259993, 259994, 259995</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>3906</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Solrød Center 4</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">267144, 267145</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>4890</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Litorinavej 2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">719361, 2202685</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>1537</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingsryds Alle 27</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">8942071</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>260</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingsryds Alle 25</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">8942075</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>540</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200016078</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200016081</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-06-26</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Solrød Center 3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">2203386</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>1115</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">200047379</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-03-29</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 51</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">8941987</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>1586</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">200055903</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingsryds Alle 1B</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2203980</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>1771</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">311156883</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-02-03</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mosevej 13B</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2204990</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>280</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">311211741</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2204674</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>355</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">311214136</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bistrupvang 36</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2188168</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>792</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">311217330</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Solrød Center 85</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2203431</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>2288</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">311217395</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingsryds Alle 3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2203441</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>839</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">311217448</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Poppelhegnet 32B</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2203865</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>501</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">311217456</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trylleskov Allé 3</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">100036252</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>1252</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">311217682</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bistrupvang 35</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2188167</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>383</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">311217631</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Solrød Center 1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2203336</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>3581</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">311217669</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindevej 15</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2187966</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>260</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">311217802</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-15</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tjørnholmvej 12</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2204117</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>875</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311217827</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-15</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 51</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">8941987</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>1690</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311224721</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 51</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">8941987</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>295</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311224732</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 51</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">8941987</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>1384</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311224734</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 51</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">8941987</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>975</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311224736</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 51</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">8941987</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>1102</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311224724</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 51</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">8941987</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>1102</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311224727</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 51</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">8941987</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>772</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311224729</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Christians Torv 124</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2190312</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>11134</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311231085</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-02-28</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Den Lille Gade 20</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">8942093</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>718</v>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311238097</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311238100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 51</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">8941987</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>308</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311238368</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 53</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">8941987</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>775</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311238367</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingsryds Alle 27</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">8942071</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>11333</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311238369</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 11</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2189961</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>719</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311238422</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 5</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2190233</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>609</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311238569</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2204674</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>1637</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311238556</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2204674</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>2297</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311238556</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2204674</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>2065</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311238556</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2204674</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>2177</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311238554</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 62</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">8941976</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>2266</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311238551</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 62</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">8941976</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>1889</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311238551</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Åsvej 14B</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">8942017</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>2149</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311238600</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engmosevej 14</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">8942071</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>1724</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311238574</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestre Grænsevej 34</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">100003759</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>431</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311238740</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Niels Juels Alle 2</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2189963</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>350</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311238698</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langager 8</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2202814</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>381</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311238728</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Højagervænget 21</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">8942087</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>1902</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311238732</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Højagervænget 21</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">8942087</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>2493</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311238734</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2204674</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>1789</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311298684</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2204674</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>1339</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311298684</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2204674</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>1448</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311298684</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havdrup Allé 6</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">7717401</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>1372</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311453702</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-08-11</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestre Odinsvej 17</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2203235</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>339</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311519279</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-10</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Salbjergvej 26</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4622</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2188346</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>328</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311549329</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,39 +3271,49 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østre Strandvej 26</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2680</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2206014</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>291</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311668910</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-24</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J55"/>
+  <autoFilter ref="A1:L55"/>
 </worksheet>
 </file>
--- a/public/exports/68534917.xlsx
+++ b/public/exports/68534917.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solrød Center 1</t>
+          <t xml:space="preserve">Litorinavej 2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203336</t>
+          <t xml:space="preserve">719361, 2202685</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H2">
-        <v>260</v>
+        <v>1537</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeparken 33A</t>
+          <t xml:space="preserve">Solrød Center 1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259943, 259944, 259945, 259946, 259947, 259949, 259956, 259982, 259950, 259951, 259952, 259953, 259954, 259955, 259957, 259958, 259960, 259961, 259962, 259963, 259964, 259965, 259966, 259967, 259968, 259969, 259971, 259972, 259973, 259974, 259975, 259976, 259977, 259978, 259979, 259980, 259989, 259990, 259991, 259993, 259994, 259995</t>
+          <t xml:space="preserve">2203336</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H3">
-        <v>3906</v>
+        <v>260</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solrød Center 4</t>
+          <t xml:space="preserve">Tingsryds Alle 27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,16 +221,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">267144, 267145</t>
+          <t xml:space="preserve">8942071</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H4">
-        <v>4890</v>
+        <v>260</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Litorinavej 2</t>
+          <t xml:space="preserve">Tingsryds Alle 25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,30 +281,30 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">719361, 2202685</t>
+          <t xml:space="preserve">8942075</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H5">
-        <v>1537</v>
+        <v>540</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200016090</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-26</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingsryds Alle 27</t>
+          <t xml:space="preserve">Solrød Center 3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,30 +341,30 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942071</t>
+          <t xml:space="preserve">2203386</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H6">
-        <v>260</v>
+        <v>1115</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200047379</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-03-29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -391,35 +391,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingsryds Alle 25</t>
+          <t xml:space="preserve">Skolevej 51</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942075</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H7">
-        <v>540</v>
+        <v>1586</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016081</t>
+          <t xml:space="preserve">200055903</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-26</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solrød Center 3</t>
+          <t xml:space="preserve">Tingsryds Alle 1B</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,25 +461,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203386</t>
+          <t xml:space="preserve">2203980</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H8">
-        <v>1115</v>
+        <v>1771</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047379</t>
+          <t xml:space="preserve">311156883</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-29</t>
+          <t xml:space="preserve">2026-02-03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -511,45 +511,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 51</t>
+          <t xml:space="preserve">Mosevej 13B</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">2204990</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H9">
-        <v>1586</v>
+        <v>280</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055903</t>
+          <t xml:space="preserve">311211741</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingsryds Alle 1B</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,35 +581,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203980</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H10">
-        <v>1771</v>
+        <v>355</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">311156883</t>
+          <t xml:space="preserve">311214136</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-03</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -631,17 +631,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosevej 13B</t>
+          <t xml:space="preserve">Bistrupvang 36</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204990</t>
+          <t xml:space="preserve">2188168</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="H11">
-        <v>280</v>
+        <v>792</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211741</t>
+          <t xml:space="preserve">311217330</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Poppelhegnet 32B</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,25 +701,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">2203865</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H12">
-        <v>355</v>
+        <v>501</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214136</t>
+          <t xml:space="preserve">311217456</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvang 36</t>
+          <t xml:space="preserve">Solrød Center 85</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188168</t>
+          <t xml:space="preserve">2203431</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -770,11 +770,11 @@
         </is>
       </c>
       <c r="H13">
-        <v>792</v>
+        <v>2288</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217330</t>
+          <t xml:space="preserve">311217395</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solrød Center 85</t>
+          <t xml:space="preserve">Tingsryds Alle 3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203431</t>
+          <t xml:space="preserve">2203441</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -830,11 +830,11 @@
         </is>
       </c>
       <c r="H14">
-        <v>2288</v>
+        <v>839</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217395</t>
+          <t xml:space="preserve">311217448</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingsryds Alle 3</t>
+          <t xml:space="preserve">Bistrupvang 35</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203441</t>
+          <t xml:space="preserve">2188167</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -890,16 +890,16 @@
         </is>
       </c>
       <c r="H15">
-        <v>839</v>
+        <v>383</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217448</t>
+          <t xml:space="preserve">311217631</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-13</t>
+          <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelhegnet 32B</t>
+          <t xml:space="preserve">Solrød Center 1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,25 +941,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203865</t>
+          <t xml:space="preserve">2203336</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H16">
-        <v>501</v>
+        <v>3581</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217456</t>
+          <t xml:space="preserve">311217669</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-13</t>
+          <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvang 35</t>
+          <t xml:space="preserve">Lindevej 15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188167</t>
+          <t xml:space="preserve">2187966</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1070,16 +1070,16 @@
         </is>
       </c>
       <c r="H18">
-        <v>383</v>
+        <v>260</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217631</t>
+          <t xml:space="preserve">311217802</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-14</t>
+          <t xml:space="preserve">2026-12-15</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solrød Center 1</t>
+          <t xml:space="preserve">Tjørnholmvej 12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203336</t>
+          <t xml:space="preserve">2204117</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1130,16 +1130,16 @@
         </is>
       </c>
       <c r="H19">
-        <v>3581</v>
+        <v>875</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217669</t>
+          <t xml:space="preserve">311217827</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-14</t>
+          <t xml:space="preserve">2026-12-15</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 15</t>
+          <t xml:space="preserve">Skolevej 51</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2187966</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="H20">
-        <v>260</v>
+        <v>1690</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217802</t>
+          <t xml:space="preserve">311224721</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-15</t>
+          <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1231,35 +1231,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 12</t>
+          <t xml:space="preserve">Skolevej 51</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204117</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H21">
-        <v>875</v>
+        <v>295</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217827</t>
+          <t xml:space="preserve">311224732</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-15</t>
+          <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1306,15 +1306,15 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H22">
-        <v>1690</v>
+        <v>1384</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224721</t>
+          <t xml:space="preserve">311224734</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1366,15 +1366,15 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H23">
-        <v>295</v>
+        <v>975</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224732</t>
+          <t xml:space="preserve">311224736</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1426,15 +1426,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H24">
-        <v>1384</v>
+        <v>1102</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224734</t>
+          <t xml:space="preserve">311224724</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1486,15 +1486,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H25">
-        <v>975</v>
+        <v>1102</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224736</t>
+          <t xml:space="preserve">311224727</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1546,15 +1546,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H26">
-        <v>1102</v>
+        <v>772</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224724</t>
+          <t xml:space="preserve">311224729</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1591,35 +1591,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 51</t>
+          <t xml:space="preserve">Christians Torv 124</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">2190312</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H27">
-        <v>1102</v>
+        <v>11134</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224727</t>
+          <t xml:space="preserve">311231085</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-26</t>
+          <t xml:space="preserve">2027-02-28</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1651,35 +1651,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 51</t>
+          <t xml:space="preserve">Den Lille Gade 20</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">8942093</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H28">
-        <v>772</v>
+        <v>718</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224729</t>
+          <t xml:space="preserve">311238100</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-26</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1711,35 +1711,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christians Torv 124</t>
+          <t xml:space="preserve">Skolevej 51</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190312</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H29">
-        <v>11134</v>
+        <v>308</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231085</t>
+          <t xml:space="preserve">311238368</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-28</t>
+          <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Den Lille Gade 20</t>
+          <t xml:space="preserve">Skolevej 53</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942093</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="H30">
-        <v>718</v>
+        <v>775</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238100</t>
+          <t xml:space="preserve">311238367</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1831,30 +1831,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 51</t>
+          <t xml:space="preserve">Tingsryds Alle 27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">8942071</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H31">
-        <v>308</v>
+        <v>11333</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238368</t>
+          <t xml:space="preserve">311238369</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 53</t>
+          <t xml:space="preserve">Engmosevej 14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">8942071</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1910,16 +1910,16 @@
         </is>
       </c>
       <c r="H32">
-        <v>775</v>
+        <v>1724</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238367</t>
+          <t xml:space="preserve">311238574</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-02</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingsryds Alle 27</t>
+          <t xml:space="preserve">Parkvej 11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942071</t>
+          <t xml:space="preserve">2189961</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1970,16 +1970,16 @@
         </is>
       </c>
       <c r="H33">
-        <v>11333</v>
+        <v>719</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238369</t>
+          <t xml:space="preserve">311238422</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-02</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 11</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,20 +2021,20 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189961</t>
+          <t xml:space="preserve">2190233</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H34">
-        <v>719</v>
+        <v>609</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238422</t>
+          <t xml:space="preserve">311238569</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2071,30 +2071,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Skolevej 62</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190233</t>
+          <t xml:space="preserve">8941976</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H35">
-        <v>609</v>
+        <v>2266</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238569</t>
+          <t xml:space="preserve">311238551</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2131,30 +2131,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Skolevej 62</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">8941976</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H36">
-        <v>1637</v>
+        <v>1889</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238556</t>
+          <t xml:space="preserve">311238551</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2206,11 +2206,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H37">
-        <v>2297</v>
+        <v>1637</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2266,11 +2266,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H38">
-        <v>2065</v>
+        <v>2297</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2326,15 +2326,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H39">
-        <v>2177</v>
+        <v>2065</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238554</t>
+          <t xml:space="preserve">311238556</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2371,30 +2371,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 62</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941976</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H40">
-        <v>2266</v>
+        <v>2177</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238551</t>
+          <t xml:space="preserve">311238554</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2431,30 +2431,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 62</t>
+          <t xml:space="preserve">Åsvej 14B</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941976</t>
+          <t xml:space="preserve">8942017</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H41">
-        <v>1889</v>
+        <v>2149</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238551</t>
+          <t xml:space="preserve">311238600</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åsvej 14B</t>
+          <t xml:space="preserve">Højagervænget 21</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942017</t>
+          <t xml:space="preserve">8942087</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2510,16 +2510,16 @@
         </is>
       </c>
       <c r="H42">
-        <v>2149</v>
+        <v>1902</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238600</t>
+          <t xml:space="preserve">311238732</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engmosevej 14</t>
+          <t xml:space="preserve">Højagervænget 21</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942071</t>
+          <t xml:space="preserve">8942087</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2570,16 +2570,16 @@
         </is>
       </c>
       <c r="H43">
-        <v>1724</v>
+        <v>2493</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238574</t>
+          <t xml:space="preserve">311238734</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Grænsevej 34</t>
+          <t xml:space="preserve">Langager 8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">100003759</t>
+          <t xml:space="preserve">2202814</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2630,11 +2630,11 @@
         </is>
       </c>
       <c r="H44">
-        <v>431</v>
+        <v>381</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238740</t>
+          <t xml:space="preserve">311238728</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langager 8</t>
+          <t xml:space="preserve">Solrød Center 4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2202814</t>
+          <t xml:space="preserve">267144, 267145</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2750,11 +2750,11 @@
         </is>
       </c>
       <c r="H46">
-        <v>381</v>
+        <v>4890</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238728</t>
+          <t xml:space="preserve">311238723</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højagervænget 21</t>
+          <t xml:space="preserve">Vestre Grænsevej 34</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942087</t>
+          <t xml:space="preserve">100003759</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2810,11 +2810,11 @@
         </is>
       </c>
       <c r="H47">
-        <v>1902</v>
+        <v>431</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238732</t>
+          <t xml:space="preserve">311238740</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højagervænget 21</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2861,25 +2861,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942087</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H48">
-        <v>2493</v>
+        <v>1789</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238734</t>
+          <t xml:space="preserve">311298684</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-04</t>
+          <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2926,11 +2926,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H49">
-        <v>1789</v>
+        <v>1339</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2986,11 +2986,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H50">
-        <v>1339</v>
+        <v>1448</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3031,35 +3031,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Havdrup Allé 6</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">7717401</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H51">
-        <v>1448</v>
+        <v>1372</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298684</t>
+          <t xml:space="preserve">311453702</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-20</t>
+          <t xml:space="preserve">2030-08-11</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,17 +3091,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havdrup Allé 6</t>
+          <t xml:space="preserve">Vestre Odinsvej 17</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7717401</t>
+          <t xml:space="preserve">2203235</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="H52">
-        <v>1372</v>
+        <v>339</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311453702</t>
+          <t xml:space="preserve">311519279</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-11</t>
+          <t xml:space="preserve">2031-05-10</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,35 +3151,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Odinsvej 17</t>
+          <t xml:space="preserve">Salbjergvej 26</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203235</t>
+          <t xml:space="preserve">2188346</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H53">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519279</t>
+          <t xml:space="preserve">311549361</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-10</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,35 +3211,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Salbjergvej 26</t>
+          <t xml:space="preserve">Østre Strandvej 26</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188346</t>
+          <t xml:space="preserve">2206014</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H54">
-        <v>328</v>
+        <v>291</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549329</t>
+          <t xml:space="preserve">311668910</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2033-03-24</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Strandvej 26</t>
+          <t xml:space="preserve">Egeparken 33A</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2206014</t>
+          <t xml:space="preserve">259943, 259944, 259945, 259946, 259947, 259949, 259956, 259982, 259950, 259951, 259952, 259953, 259954, 259955, 259957, 259958, 259960, 259961, 259962, 259963, 259964, 259965, 259966, 259967, 259968, 259969, 259971, 259972, 259973, 259974, 259975, 259976, 259977, 259978, 259979, 259980, 259989, 259990, 259991, 259993, 259994, 259995</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H55">
-        <v>291</v>
+        <v>3906</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668910</t>
+          <t xml:space="preserve">311903759</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-24</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">

--- a/public/exports/68534917.xlsx
+++ b/public/exports/68534917.xlsx
@@ -294,7 +294,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016090</t>
+          <t xml:space="preserve">200016081</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/public/exports/68534917.xlsx
+++ b/public/exports/68534917.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:M55"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -299,15 +319,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strunge Jensen A/S</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-26</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -359,15 +384,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-29</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -419,15 +449,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t xml:space="preserve">TopDahl ApS</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -479,15 +514,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-03</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -539,15 +579,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -599,15 +644,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -659,15 +709,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -719,15 +774,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-15</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-15</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-28</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-11</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-10</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3174,20 +3434,25 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549361</t>
+          <t xml:space="preserve">311549329</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">ISOLINK ApS</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-24</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,21 +3569,26 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bang &amp; Beenfeldt A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L55"/>
+  <autoFilter ref="A1:M55"/>
 </worksheet>
 </file>
--- a/public/exports/68534917.xlsx
+++ b/public/exports/68534917.xlsx
@@ -314,7 +314,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016081</t>
+          <t xml:space="preserve">200016078</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238100</t>
+          <t xml:space="preserve">311238097</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
